--- a/modules/40_q3/figures/editable/origin_templates/data/23_Si多初值局部盆地气泡图.xlsx
+++ b/modules/40_q3/figures/editable/origin_templates/data/23_Si多初值局部盆地气泡图.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="1" r:id="Rac34a15d5a8a4a5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="1" r:id="Rd9b8d988427d4b3f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -286,224 +286,343 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>拟合口径(颜色分组)</x:v>
+        <x:v>入射角(度)(颜色分组)</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>初值序号(X)</x:v>
+        <x:v>最终厚度(μm)(X)</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>厚度(μm)(Y)</x:v>
+        <x:v>RMSE(百分点)(Y)</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>RMSE(百分点)(气泡大小)</x:v>
+        <x:v>初值序号(标签)</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>收敛状态(标签)</x:v>
+        <x:v>边界命中(辅助)</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="2" t="str">
-        <x:v>10度Airy</x:v>
+      <x:c r="A2" s="2" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="2" t="n">
+        <x:v>2.5142983211173155</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="n">
+        <x:v>3.29228661951797</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="n">
-        <x:v>2.514823016730237</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="n">
-        <x:v>3.2888687737742983</x:v>
-      </x:c>
       <x:c r="E2" s="2" t="str">
-        <x:v>收敛</x:v>
+        <x:v>log10_carrier_cm3;log10_collision_s-1</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
-        <x:v>10度Airy</x:v>
+      <x:c r="A3" s="2" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="2" t="n">
+        <x:v>3.2242127479639167</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="n">
+        <x:v>1.89931839660466</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="n">
-        <x:v>3.2242631933931745</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="n">
-        <x:v>1.8997958614626724</x:v>
-      </x:c>
       <x:c r="E3" s="2" t="str">
-        <x:v>收敛</x:v>
+        <x:v>log10_carrier_cm3;log10_collision_s-1</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="2" t="str">
-        <x:v>10度Airy</x:v>
+      <x:c r="A4" s="2" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="2" t="n">
+        <x:v>3.2474353562410494</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="n">
+        <x:v>1.874502062338921</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C4" s="2" t="n">
-        <x:v>3.2479974043972195</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="n">
-        <x:v>1.8738296801551615</x:v>
-      </x:c>
       <x:c r="E4" s="2" t="str">
-        <x:v>收敛</x:v>
+        <x:v>log10_collision_s-1</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="2" t="str">
-        <x:v>10度Airy</x:v>
+      <x:c r="A5" s="2" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="2" t="n">
+        <x:v>3.2474355258222887</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="n">
+        <x:v>1.8745020623394468</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C5" s="2" t="n">
-        <x:v>3.2479974100186757</x:v>
-      </x:c>
-      <x:c r="D5" s="2" t="n">
-        <x:v>1.8738296801546928</x:v>
-      </x:c>
       <x:c r="E5" s="2" t="str">
-        <x:v>收敛</x:v>
+        <x:v>log10_collision_s-1</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="2" t="str">
-        <x:v>10度Airy</x:v>
+      <x:c r="A6" s="2" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="2" t="n">
+        <x:v>3.2474353632212205</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="n">
+        <x:v>1.874502062338223</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C6" s="2" t="n">
-        <x:v>3.247997417105262</x:v>
-      </x:c>
-      <x:c r="D6" s="2" t="n">
-        <x:v>1.8738296801541603</x:v>
-      </x:c>
       <x:c r="E6" s="2" t="str">
-        <x:v>收敛</x:v>
+        <x:v>log10_collision_s-1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="2" t="str">
-        <x:v>10度Airy</x:v>
+      <x:c r="A7" s="2" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="2" t="n">
+        <x:v>3.2242127454110387</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="n">
+        <x:v>1.8993183966046638</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="2" t="n">
-        <x:v>3.2242631912535646</x:v>
-      </x:c>
-      <x:c r="D7" s="2" t="n">
-        <x:v>1.899795861462676</x:v>
-      </x:c>
       <x:c r="E7" s="2" t="str">
-        <x:v>收敛</x:v>
+        <x:v>log10_carrier_cm3;log10_collision_s-1</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="2" t="str">
-        <x:v>15度Airy</x:v>
+      <x:c r="A8" s="2" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B8" s="2" t="n">
+        <x:v>3.187475152277794</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="n">
+        <x:v>3.363815918763196</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C8" s="2" t="n">
-        <x:v>3.187519634509146</x:v>
-      </x:c>
-      <x:c r="D8" s="2" t="n">
-        <x:v>3.355382352363833</x:v>
-      </x:c>
       <x:c r="E8" s="2" t="str">
-        <x:v>收敛</x:v>
+        <x:v>log10_carrier_cm3;log10_collision_s-1</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="2" t="str">
-        <x:v>15度Airy</x:v>
+      <x:c r="A9" s="2" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="2" t="n">
+        <x:v>3.1874753640476907</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="n">
+        <x:v>3.3638159187634207</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C9" s="2" t="n">
-        <x:v>3.18751984899386</x:v>
-      </x:c>
-      <x:c r="D9" s="2" t="n">
-        <x:v>3.3553823523639568</x:v>
-      </x:c>
       <x:c r="E9" s="2" t="str">
-        <x:v>收敛</x:v>
+        <x:v>log10_carrier_cm3;log10_collision_s-1</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="2" t="str">
-        <x:v>15度Airy</x:v>
+      <x:c r="A10" s="2" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B10" s="2" t="n">
+        <x:v>3.187475321959225</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="n">
+        <x:v>3.3638159566019112</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C10" s="2" t="n">
-        <x:v>3.1875198075375044</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="n">
-        <x:v>3.355382389985421</x:v>
-      </x:c>
       <x:c r="E10" s="2" t="str">
-        <x:v>收敛</x:v>
+        <x:v>log10_carrier_cm3;log10_collision_s-1</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="2" t="str">
-        <x:v>15度Airy</x:v>
+      <x:c r="A11" s="2" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="2" t="n">
+        <x:v>3.187475203652208</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="n">
+        <x:v>3.363815956601899</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C11" s="2" t="n">
-        <x:v>3.1875196908655554</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="n">
-        <x:v>3.355382389985408</x:v>
-      </x:c>
       <x:c r="E11" s="2" t="str">
-        <x:v>收敛</x:v>
+        <x:v>log10_carrier_cm3;log10_collision_s-1</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="2" t="str">
-        <x:v>15度Airy</x:v>
+      <x:c r="A12" s="2" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B12" s="2" t="n">
+        <x:v>3.1874751796336294</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="n">
+        <x:v>3.3638159187627887</x:v>
+      </x:c>
+      <x:c r="D12" s="2" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C12" s="2" t="n">
-        <x:v>3.187519666375829</x:v>
-      </x:c>
-      <x:c r="D12" s="2" t="n">
-        <x:v>3.3553823523633466</x:v>
-      </x:c>
       <x:c r="E12" s="2" t="str">
-        <x:v>收敛</x:v>
+        <x:v>log10_carrier_cm3;log10_collision_s-1</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="2" t="str">
-        <x:v>15度Airy</x:v>
+      <x:c r="A13" s="2" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B13" s="2" t="n">
+        <x:v>3.3537830755836113</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="n">
+        <x:v>5.074979332517187</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C13" s="2" t="n">
-        <x:v>3.353875718354043</x:v>
-      </x:c>
-      <x:c r="D13" s="2" t="n">
-        <x:v>5.066709886477225</x:v>
-      </x:c>
       <x:c r="E13" s="2" t="str">
-        <x:v>收敛</x:v>
-      </x:c>
+        <x:v>substrate_index;log10_carrier_cm3;log10_collision_s-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
